--- a/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1276"/>
+  <dimension ref="A1:C1339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19588,6 +19588,857 @@
         <v>265</v>
       </c>
     </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aarnink a 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1277" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1278" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1279" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1280" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1281" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1282" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alt p 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1283" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aarnink a 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1284" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sather a 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1285" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sather a 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1286" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1287" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schwengers p 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1288" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schwengers p 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1289" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aytekin d 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1290" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
+        </is>
+      </c>
+      <c r="C1291" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
+        </is>
+      </c>
+      <c r="C1292" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr"/>
+      <c r="C1293" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr"/>
+      <c r="C1294" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr"/>
+      <c r="C1295" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
+        </is>
+      </c>
+      <c r="C1296" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
+        </is>
+      </c>
+      <c r="C1297" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr"/>
+      <c r="C1298" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
+        </is>
+      </c>
+      <c r="C1299" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr"/>
+      <c r="C1300" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
+        </is>
+      </c>
+      <c r="C1301" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion lohmuhle
+  lubeck </t>
+        </is>
+      </c>
+      <c r="C1302" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
+        </is>
+      </c>
+      <c r="C1303" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
+        </is>
+      </c>
+      <c r="C1304" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr"/>
+      <c r="C1305" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
+        </is>
+      </c>
+      <c r="C1306" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr"/>
+      <c r="C1308" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr"/>
+      <c r="C1309" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr"/>
+      <c r="C1311" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr"/>
+      <c r="C1313" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>E3xs5mIe</t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr"/>
+      <c r="C1319" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr"/>
+      <c r="C1320" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr"/>
+      <c r="C1321" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr"/>
+      <c r="C1322" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr"/>
+      <c r="C1323" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr"/>
+      <c r="C1324" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr"/>
+      <c r="C1325" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr"/>
+      <c r="C1326" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr"/>
+      <c r="C1327" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr"/>
+      <c r="C1328" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr"/>
+      <c r="C1329" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr"/>
+      <c r="C1330" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr"/>
+      <c r="C1331" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr"/>
+      <c r="C1332" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr"/>
+      <c r="C1333" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr"/>
+      <c r="C1334" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr"/>
+      <c r="C1335" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr"/>
+      <c r="C1336" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr"/>
+      <c r="C1337" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr"/>
+      <c r="C1338" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr"/>
+      <c r="C1339" t="n">
+        <v>382</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1339"/>
+  <dimension ref="A1:C1360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20439,6 +20439,237 @@
         <v>382</v>
       </c>
     </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr"/>
+      <c r="C1340" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr"/>
+      <c r="C1341" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr"/>
+      <c r="C1342" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr"/>
+      <c r="C1343" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr"/>
+      <c r="C1344" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr"/>
+      <c r="C1345" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr"/>
+      <c r="C1346" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr"/>
+      <c r="C1347" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr"/>
+      <c r="C1348" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr"/>
+      <c r="C1349" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr"/>
+      <c r="C1350" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr"/>
+      <c r="C1351" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr"/>
+      <c r="C1352" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr"/>
+      <c r="C1353" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr"/>
+      <c r="C1354" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr"/>
+      <c r="C1355" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr"/>
+      <c r="C1356" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr"/>
+      <c r="C1357" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr"/>
+      <c r="C1358" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr"/>
+      <c r="C1359" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr"/>
+      <c r="C1360" t="n">
+        <v>383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1360"/>
+  <dimension ref="A1:C1399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20670,6 +20670,490 @@
         <v>383</v>
       </c>
     </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr"/>
+      <c r="C1368" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr"/>
+      <c r="C1369" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr"/>
+      <c r="C1370" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr"/>
+      <c r="C1374" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr"/>
+      <c r="C1376" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr"/>
+      <c r="C1377" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr"/>
+      <c r="C1378" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr"/>
+      <c r="C1379" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr"/>
+      <c r="C1380" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr"/>
+      <c r="C1381" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr"/>
+      <c r="C1382" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr"/>
+      <c r="C1383" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr"/>
+      <c r="C1384" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr"/>
+      <c r="C1385" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr"/>
+      <c r="C1386" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr"/>
+      <c r="C1387" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr"/>
+      <c r="C1388" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr"/>
+      <c r="C1389" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr"/>
+      <c r="C1390" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr"/>
+      <c r="C1391" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr"/>
+      <c r="C1392" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr"/>
+      <c r="C1393" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr"/>
+      <c r="C1394" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr"/>
+      <c r="C1395" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr"/>
+      <c r="C1396" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr"/>
+      <c r="C1397" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr"/>
+      <c r="C1398" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr"/>
+      <c r="C1399" t="n">
+        <v>384</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1399"/>
+  <dimension ref="A1:C1428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21154,6 +21154,325 @@
         <v>384</v>
       </c>
     </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr"/>
+      <c r="C1400" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr"/>
+      <c r="C1401" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr"/>
+      <c r="C1402" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr"/>
+      <c r="C1403" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr"/>
+      <c r="C1404" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr"/>
+      <c r="C1405" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr"/>
+      <c r="C1406" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr"/>
+      <c r="C1407" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr"/>
+      <c r="C1408" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr"/>
+      <c r="C1409" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr"/>
+      <c r="C1410" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr"/>
+      <c r="C1411" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr"/>
+      <c r="C1412" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr"/>
+      <c r="C1413" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr"/>
+      <c r="C1414" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr"/>
+      <c r="C1415" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr"/>
+      <c r="C1416" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr"/>
+      <c r="C1417" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr"/>
+      <c r="C1418" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr"/>
+      <c r="C1419" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr"/>
+      <c r="C1420" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr"/>
+      <c r="C1421" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr"/>
+      <c r="C1422" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr"/>
+      <c r="C1423" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr"/>
+      <c r="C1424" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr"/>
+      <c r="C1425" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr"/>
+      <c r="C1426" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr"/>
+      <c r="C1427" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr"/>
+      <c r="C1428" t="n">
+        <v>385</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
